--- a/Co_so_phan_loai_nganh_HOSE.xlsx
+++ b/Co_so_phan_loai_nganh_HOSE.xlsx
@@ -477,7 +477,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>[dd/mm/yyyy]</t>
+          <t>03/06/2026</t>
         </is>
       </c>
     </row>
